--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260624.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260624.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>18.37%</t>
+          <t>17.78%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>74,000,000</t>
+          <t>74,600,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.19%</t>
+          <t>7.66%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>5.86%</t>
+          <t>6.08%</t>
         </is>
       </c>
     </row>
@@ -682,51 +682,51 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.99%</t>
+          <t>4.81%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>38,800,000</t>
+          <t>3,250,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.69%</t>
+          <t>4.74%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>3,250,000</t>
+          <t>38,800,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.51%</t>
+          <t>4.59%</t>
         </is>
       </c>
     </row>
@@ -748,51 +748,51 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.40%</t>
+          <t>4.33%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>1,400,000</t>
+          <t>940,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>3.89%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>1,435,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.55%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>4,700,000</t>
+          <t>4,200,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.40%</t>
+          <t>3.04%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
@@ -924,46 +924,46 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>4,500,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>1,700,000</t>
+          <t>4,500,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.62%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
@@ -1034,73 +1034,73 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>430,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>430,000</t>
+          <t>9,911,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>279,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
@@ -1122,29 +1122,29 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>9,911,000</t>
+          <t>279,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1166,95 +1166,95 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>1,950,000</t>
+          <t>1,800,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>390,000</t>
+          <t>1,950,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>南亞</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>7,550,000</t>
+          <t>390,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>南亞</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,572,000</t>
+          <t>7,550,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -1276,46 +1276,46 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.64%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>450,000</t>
+          <t>570,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>570,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,22 +1327,22 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>450,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.41%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1459,34 +1459,34 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>900,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -1496,46 +1496,46 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.34%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>240,000</t>
+          <t>900,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,22 +1547,22 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>160,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>穩懋</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>穩懋</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>7,159,736,723</t>
+          <t>4,523,475,393</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>2,623,797,531</t>
+          <t>-27,843,602</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
